--- a/lecture_slides/10_chapter_simple_regression/data/autoparts_regression.xlsx
+++ b/lecture_slides/10_chapter_simple_regression/data/autoparts_regression.xlsx
@@ -365,27 +365,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>sales2012_k</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>population_3mi</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>income_3mi</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>yelp_rating</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>endcap</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sales2012_k</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>population_3mi</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>income_3mi</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>yelp_rating</t>
         </is>
       </c>
     </row>
@@ -394,19 +394,19 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>1761</v>
       </c>
       <c r="C2">
-        <v>1651</v>
+        <v>15432</v>
       </c>
       <c r="D2">
-        <v>15432</v>
+        <v>47644</v>
       </c>
       <c r="E2">
-        <v>47644</v>
+        <v>1.5</v>
       </c>
       <c r="F2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -414,19 +414,19 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3493</v>
       </c>
       <c r="C3">
-        <v>3517</v>
+        <v>51425</v>
       </c>
       <c r="D3">
-        <v>51425</v>
+        <v>31273</v>
       </c>
       <c r="E3">
-        <v>31273</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -434,19 +434,19 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3450</v>
       </c>
       <c r="C4">
-        <v>3431</v>
+        <v>54496</v>
       </c>
       <c r="D4">
-        <v>54496</v>
+        <v>67161</v>
       </c>
       <c r="E4">
-        <v>67161</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -454,16 +454,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>1445</v>
       </c>
       <c r="C5">
-        <v>1328</v>
+        <v>63234</v>
       </c>
       <c r="D5">
-        <v>63234</v>
+        <v>47911</v>
       </c>
       <c r="E5">
-        <v>47911</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -474,19 +474,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4458</v>
       </c>
       <c r="C6">
-        <v>4677</v>
+        <v>64222</v>
       </c>
       <c r="D6">
-        <v>64222</v>
+        <v>49429</v>
       </c>
       <c r="E6">
-        <v>49429</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -494,19 +494,19 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>4502</v>
       </c>
       <c r="C7">
-        <v>4699</v>
+        <v>76547</v>
       </c>
       <c r="D7">
-        <v>76547</v>
+        <v>91781</v>
       </c>
       <c r="E7">
-        <v>91781</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -514,19 +514,19 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>3666</v>
       </c>
       <c r="C8">
-        <v>3704</v>
+        <v>81091</v>
       </c>
       <c r="D8">
-        <v>81091</v>
+        <v>45834</v>
       </c>
       <c r="E8">
-        <v>45834</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -534,19 +534,19 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>3844</v>
       </c>
       <c r="C9">
-        <v>3907</v>
+        <v>81495</v>
       </c>
       <c r="D9">
-        <v>81495</v>
+        <v>61567</v>
       </c>
       <c r="E9">
-        <v>61567</v>
+        <v>4.5</v>
       </c>
       <c r="F9">
-        <v>4.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -554,19 +554,19 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2549</v>
       </c>
       <c r="C10">
-        <v>2441</v>
+        <v>99660</v>
       </c>
       <c r="D10">
-        <v>99660</v>
+        <v>54657</v>
       </c>
       <c r="E10">
-        <v>54657</v>
+        <v>2.5</v>
       </c>
       <c r="F10">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -574,19 +574,19 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2705</v>
       </c>
       <c r="C11">
-        <v>2550</v>
+        <v>102122</v>
       </c>
       <c r="D11">
-        <v>102122</v>
+        <v>53474</v>
       </c>
       <c r="E11">
-        <v>53474</v>
+        <v>2.5</v>
       </c>
       <c r="F11">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -594,19 +594,19 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>3829</v>
       </c>
       <c r="C12">
-        <v>3887</v>
+        <v>111246</v>
       </c>
       <c r="D12">
-        <v>111246</v>
+        <v>61989</v>
       </c>
       <c r="E12">
-        <v>61989</v>
+        <v>4.5</v>
       </c>
       <c r="F12">
-        <v>4.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -614,19 +614,19 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>4850</v>
       </c>
       <c r="C13">
-        <v>5112</v>
+        <v>116345</v>
       </c>
       <c r="D13">
-        <v>116345</v>
+        <v>56149</v>
       </c>
       <c r="E13">
-        <v>56149</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -634,19 +634,19 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>4467</v>
       </c>
       <c r="C14">
-        <v>4677</v>
+        <v>118329</v>
       </c>
       <c r="D14">
-        <v>118329</v>
+        <v>58673</v>
       </c>
       <c r="E14">
-        <v>58673</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -654,19 +654,19 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>3089</v>
       </c>
       <c r="C15">
-        <v>2933</v>
+        <v>120915</v>
       </c>
       <c r="D15">
-        <v>120915</v>
+        <v>26588</v>
       </c>
       <c r="E15">
-        <v>26588</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -674,19 +674,19 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>4523</v>
       </c>
       <c r="C16">
-        <v>4733</v>
+        <v>133281</v>
       </c>
       <c r="D16">
-        <v>133281</v>
+        <v>68709</v>
       </c>
       <c r="E16">
-        <v>68709</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -694,19 +694,19 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>4401</v>
       </c>
       <c r="C17">
-        <v>4607</v>
+        <v>135325</v>
       </c>
       <c r="D17">
-        <v>135325</v>
+        <v>48502</v>
       </c>
       <c r="E17">
-        <v>48502</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -714,19 +714,19 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>3586</v>
       </c>
       <c r="C18">
-        <v>3375</v>
+        <v>150982</v>
       </c>
       <c r="D18">
-        <v>150982</v>
+        <v>33792</v>
       </c>
       <c r="E18">
-        <v>33792</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -734,19 +734,19 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>1949</v>
       </c>
       <c r="C19">
-        <v>1764</v>
+        <v>182381</v>
       </c>
       <c r="D19">
-        <v>182381</v>
+        <v>35875</v>
       </c>
       <c r="E19">
-        <v>35875</v>
+        <v>1.5</v>
       </c>
       <c r="F19">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -754,19 +754,19 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>4219</v>
       </c>
       <c r="C20">
-        <v>4360</v>
+        <v>387887</v>
       </c>
       <c r="D20">
-        <v>387887</v>
+        <v>39480</v>
       </c>
       <c r="E20">
-        <v>39480</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -774,19 +774,19 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>3469</v>
       </c>
       <c r="C21">
-        <v>3444</v>
+        <v>389167</v>
       </c>
       <c r="D21">
-        <v>389167</v>
+        <v>38821</v>
       </c>
       <c r="E21">
-        <v>38821</v>
+        <v>4</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -794,19 +794,19 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2511</v>
       </c>
       <c r="C22">
-        <v>2285</v>
+        <v>396904</v>
       </c>
       <c r="D22">
-        <v>396904</v>
+        <v>38957</v>
       </c>
       <c r="E22">
-        <v>38957</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -814,19 +814,19 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2750</v>
       </c>
       <c r="C23">
-        <v>2734</v>
+        <v>459473</v>
       </c>
       <c r="D23">
-        <v>459473</v>
+        <v>47320</v>
       </c>
       <c r="E23">
-        <v>47320</v>
+        <v>3</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -834,19 +834,19 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>2789</v>
       </c>
       <c r="C24">
-        <v>2496</v>
+        <v>527877</v>
       </c>
       <c r="D24">
-        <v>527877</v>
+        <v>51200</v>
       </c>
       <c r="E24">
-        <v>51200</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -854,19 +854,19 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2916</v>
       </c>
       <c r="C25">
-        <v>2631</v>
+        <v>27486</v>
       </c>
       <c r="D25">
-        <v>27486</v>
+        <v>110148</v>
       </c>
       <c r="E25">
-        <v>110148</v>
+        <v>4</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -874,19 +874,19 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2267</v>
       </c>
       <c r="C26">
-        <v>2165</v>
+        <v>35436</v>
       </c>
       <c r="D26">
-        <v>35436</v>
+        <v>64938</v>
       </c>
       <c r="E26">
-        <v>64938</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -894,19 +894,19 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>3139</v>
       </c>
       <c r="C27">
-        <v>2869</v>
+        <v>36788</v>
       </c>
       <c r="D27">
-        <v>36788</v>
+        <v>78608</v>
       </c>
       <c r="E27">
-        <v>78608</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -914,19 +914,19 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>1939</v>
       </c>
       <c r="C28">
-        <v>1926</v>
+        <v>65415</v>
       </c>
       <c r="D28">
-        <v>65415</v>
+        <v>50281</v>
       </c>
       <c r="E28">
-        <v>50281</v>
+        <v>2.5</v>
       </c>
       <c r="F28">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -934,19 +934,19 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>3668</v>
       </c>
       <c r="C29">
-        <v>3291</v>
+        <v>66395</v>
       </c>
       <c r="D29">
-        <v>66395</v>
+        <v>82936</v>
       </c>
       <c r="E29">
-        <v>82936</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -954,19 +954,19 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>2645</v>
       </c>
       <c r="C30">
-        <v>2302</v>
+        <v>80210</v>
       </c>
       <c r="D30">
-        <v>80210</v>
+        <v>58287</v>
       </c>
       <c r="E30">
-        <v>58287</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -974,19 +974,19 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>1878</v>
       </c>
       <c r="C31">
-        <v>1913</v>
+        <v>81438</v>
       </c>
       <c r="D31">
-        <v>81438</v>
+        <v>65130</v>
       </c>
       <c r="E31">
-        <v>65130</v>
+        <v>2.5</v>
       </c>
       <c r="F31">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -994,19 +994,19 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>1556</v>
       </c>
       <c r="C32">
-        <v>1681</v>
+        <v>105833</v>
       </c>
       <c r="D32">
-        <v>105833</v>
+        <v>88587</v>
       </c>
       <c r="E32">
-        <v>88587</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1014,19 +1014,19 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="C33">
-        <v>1272</v>
+        <v>109139</v>
       </c>
       <c r="D33">
-        <v>109139</v>
+        <v>106508</v>
       </c>
       <c r="E33">
-        <v>106508</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1034,19 +1034,19 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="C34">
-        <v>2128</v>
+        <v>110247</v>
       </c>
       <c r="D34">
-        <v>110247</v>
+        <v>73393</v>
       </c>
       <c r="E34">
-        <v>73393</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1054,19 +1054,19 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>2441</v>
       </c>
       <c r="C35">
-        <v>2362</v>
+        <v>115501</v>
       </c>
       <c r="D35">
-        <v>115501</v>
+        <v>66667</v>
       </c>
       <c r="E35">
-        <v>66667</v>
+        <v>3.5</v>
       </c>
       <c r="F35">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1074,19 +1074,19 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>1950</v>
       </c>
       <c r="C36">
-        <v>2069</v>
+        <v>121059</v>
       </c>
       <c r="D36">
-        <v>121059</v>
+        <v>56754</v>
       </c>
       <c r="E36">
-        <v>56754</v>
+        <v>3</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1094,19 +1094,19 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>848</v>
       </c>
       <c r="C37">
-        <v>1059</v>
+        <v>125624</v>
       </c>
       <c r="D37">
-        <v>125624</v>
+        <v>60894</v>
       </c>
       <c r="E37">
-        <v>60894</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1114,19 +1114,19 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>1560</v>
       </c>
       <c r="C38">
-        <v>1691</v>
+        <v>127477</v>
       </c>
       <c r="D38">
-        <v>127477</v>
+        <v>73027</v>
       </c>
       <c r="E38">
-        <v>73027</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1134,19 +1134,19 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>1443</v>
       </c>
       <c r="C39">
-        <v>1399</v>
+        <v>156559</v>
       </c>
       <c r="D39">
-        <v>156559</v>
+        <v>63554</v>
       </c>
       <c r="E39">
-        <v>63554</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1154,19 +1154,19 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>1555</v>
       </c>
       <c r="C40">
-        <v>1695</v>
+        <v>163039</v>
       </c>
       <c r="D40">
-        <v>163039</v>
+        <v>36416</v>
       </c>
       <c r="E40">
-        <v>36416</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1174,19 +1174,19 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1365</v>
       </c>
       <c r="C41">
-        <v>1502</v>
+        <v>171086</v>
       </c>
       <c r="D41">
-        <v>171086</v>
+        <v>63085</v>
       </c>
       <c r="E41">
-        <v>63085</v>
+        <v>1.5</v>
       </c>
       <c r="F41">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1194,19 +1194,19 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2145</v>
       </c>
       <c r="C42">
-        <v>2148</v>
+        <v>192373</v>
       </c>
       <c r="D42">
-        <v>192373</v>
+        <v>44851</v>
       </c>
       <c r="E42">
-        <v>44851</v>
+        <v>3</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1214,19 +1214,19 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>2343</v>
       </c>
       <c r="C43">
-        <v>2033</v>
+        <v>193961</v>
       </c>
       <c r="D43">
-        <v>193961</v>
+        <v>69780</v>
       </c>
       <c r="E43">
-        <v>69780</v>
+        <v>2.5</v>
       </c>
       <c r="F43">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1234,19 +1234,19 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>1169</v>
       </c>
       <c r="C44">
-        <v>1460</v>
+        <v>250989</v>
       </c>
       <c r="D44">
-        <v>250989</v>
+        <v>60684</v>
       </c>
       <c r="E44">
-        <v>60684</v>
+        <v>1.5</v>
       </c>
       <c r="F44">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1254,19 +1254,19 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>1476</v>
       </c>
       <c r="C45">
-        <v>1690</v>
+        <v>380860</v>
       </c>
       <c r="D45">
-        <v>380860</v>
+        <v>62821</v>
       </c>
       <c r="E45">
-        <v>62821</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1274,19 +1274,19 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>2232</v>
       </c>
       <c r="C46">
-        <v>2186</v>
+        <v>386399</v>
       </c>
       <c r="D46">
-        <v>386399</v>
+        <v>44625</v>
       </c>
       <c r="E46">
-        <v>44625</v>
+        <v>3</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>332.77</v>
+        <v>355.61</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>757.51</v>
+        <v>751.88</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.9135</v>
+        <v>0.9262</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.8344</v>
+        <v>0.8579</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>463.7</v>
+        <v>420.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>14.72</v>
+        <v>16.11</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>51.457</v>
+        <v>46.659</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>2.13E-18</v>
+        <v>7.82E-20</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>216.71</v>
+        <v>259.67</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>653.7</v>
+        <v>657.8</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>861.3</v>
+        <v>846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>3741.6</v>
+        <v>3739.1</v>
       </c>
     </row>
     <row r="4">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>98.61</v>
+        <v>89.41</v>
       </c>
     </row>
     <row r="6">
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>474.06</v>
+        <v>429.85</v>
       </c>
     </row>
     <row r="7">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>3542.7</v>
+        <v>3558.8</v>
       </c>
     </row>
     <row r="8">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>3940.4</v>
+        <v>3919.4</v>
       </c>
     </row>
     <row r="9">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>2785.6</v>
+        <v>2872.2</v>
       </c>
     </row>
     <row r="10">
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>4697.6</v>
+        <v>4606</v>
       </c>
     </row>
   </sheetData>
@@ -1626,27 +1626,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>sales2012_k</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>population_3mi</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>income_3mi</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>yelp_rating</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>endcap</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sales2012_k</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>population_3mi</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>income_3mi</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>yelp_rating</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -1670,28 +1670,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>1761</v>
       </c>
       <c r="C2">
-        <v>1651</v>
+        <v>15432</v>
       </c>
       <c r="D2">
-        <v>15432</v>
+        <v>47644</v>
       </c>
       <c r="E2">
-        <v>47644</v>
+        <v>1.5</v>
       </c>
       <c r="F2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>1469</v>
+        <v>1483.4</v>
       </c>
       <c r="H2">
-        <v>182</v>
+        <v>277.6</v>
       </c>
       <c r="I2">
-        <v>0.404</v>
+        <v>0.668</v>
       </c>
     </row>
     <row r="3">
@@ -1699,28 +1699,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3493</v>
       </c>
       <c r="C3">
-        <v>3517</v>
+        <v>51425</v>
       </c>
       <c r="D3">
-        <v>51425</v>
+        <v>31273</v>
       </c>
       <c r="E3">
-        <v>31273</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3362.8</v>
+        <v>3363.1</v>
       </c>
       <c r="H3">
-        <v>154.2</v>
+        <v>129.9</v>
       </c>
       <c r="I3">
-        <v>0.338</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="4">
@@ -1728,28 +1728,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3450</v>
       </c>
       <c r="C4">
-        <v>3431</v>
+        <v>54496</v>
       </c>
       <c r="D4">
-        <v>54496</v>
+        <v>67161</v>
       </c>
       <c r="E4">
-        <v>67161</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>3362.8</v>
+        <v>3363.1</v>
       </c>
       <c r="H4">
-        <v>68.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I4">
-        <v>0.149</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="5">
@@ -1757,28 +1757,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>1445</v>
       </c>
       <c r="C5">
-        <v>1328</v>
+        <v>63234</v>
       </c>
       <c r="D5">
-        <v>63234</v>
+        <v>47911</v>
       </c>
       <c r="E5">
-        <v>47911</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1090.3</v>
+        <v>1107.5</v>
       </c>
       <c r="H5">
-        <v>237.7</v>
+        <v>337.5</v>
       </c>
       <c r="I5">
-        <v>0.534</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1786,28 +1786,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4458</v>
       </c>
       <c r="C6">
-        <v>4677</v>
+        <v>64222</v>
       </c>
       <c r="D6">
-        <v>64222</v>
+        <v>49429</v>
       </c>
       <c r="E6">
-        <v>49429</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>4120.3</v>
+        <v>4115</v>
       </c>
       <c r="H6">
-        <v>556.7</v>
+        <v>343</v>
       </c>
       <c r="I6">
-        <v>1.242</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="7">
@@ -1815,28 +1815,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>4502</v>
       </c>
       <c r="C7">
-        <v>4699</v>
+        <v>76547</v>
       </c>
       <c r="D7">
-        <v>76547</v>
+        <v>91781</v>
       </c>
       <c r="E7">
-        <v>91781</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>4120.3</v>
+        <v>4115</v>
       </c>
       <c r="H7">
-        <v>578.7</v>
+        <v>387</v>
       </c>
       <c r="I7">
-        <v>1.291</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="8">
@@ -1844,28 +1844,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>3666</v>
       </c>
       <c r="C8">
-        <v>3704</v>
+        <v>81091</v>
       </c>
       <c r="D8">
-        <v>81091</v>
+        <v>45834</v>
       </c>
       <c r="E8">
-        <v>45834</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>3362.8</v>
+        <v>3363.1</v>
       </c>
       <c r="H8">
-        <v>341.2</v>
+        <v>302.9</v>
       </c>
       <c r="I8">
-        <v>0.748</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="9">
@@ -1873,28 +1873,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>3844</v>
       </c>
       <c r="C9">
-        <v>3907</v>
+        <v>81495</v>
       </c>
       <c r="D9">
-        <v>81495</v>
+        <v>61567</v>
       </c>
       <c r="E9">
-        <v>61567</v>
+        <v>4.5</v>
       </c>
       <c r="F9">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>3741.6</v>
+        <v>3739.1</v>
       </c>
       <c r="H9">
-        <v>165.4</v>
+        <v>104.9</v>
       </c>
       <c r="I9">
-        <v>0.365</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="10">
@@ -1902,28 +1902,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2549</v>
       </c>
       <c r="C10">
-        <v>2441</v>
+        <v>99660</v>
       </c>
       <c r="D10">
-        <v>99660</v>
+        <v>54657</v>
       </c>
       <c r="E10">
-        <v>54657</v>
+        <v>2.5</v>
       </c>
       <c r="F10">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>2226.6</v>
+        <v>2235.3</v>
       </c>
       <c r="H10">
-        <v>214.4</v>
+        <v>313.7</v>
       </c>
       <c r="I10">
-        <v>0.469</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="11">
@@ -1931,28 +1931,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2705</v>
       </c>
       <c r="C11">
-        <v>2550</v>
+        <v>102122</v>
       </c>
       <c r="D11">
-        <v>102122</v>
+        <v>53474</v>
       </c>
       <c r="E11">
-        <v>53474</v>
+        <v>2.5</v>
       </c>
       <c r="F11">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>2226.6</v>
+        <v>2235.3</v>
       </c>
       <c r="H11">
-        <v>323.4</v>
+        <v>469.7</v>
       </c>
       <c r="I11">
-        <v>0.707</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="12">
@@ -1960,28 +1960,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>3829</v>
       </c>
       <c r="C12">
-        <v>3887</v>
+        <v>111246</v>
       </c>
       <c r="D12">
-        <v>111246</v>
+        <v>61989</v>
       </c>
       <c r="E12">
-        <v>61989</v>
+        <v>4.5</v>
       </c>
       <c r="F12">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>3741.6</v>
+        <v>3739.1</v>
       </c>
       <c r="H12">
-        <v>145.4</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I12">
-        <v>0.321</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="13">
@@ -1989,28 +1989,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>4850</v>
       </c>
       <c r="C13">
-        <v>5112</v>
+        <v>116345</v>
       </c>
       <c r="D13">
-        <v>116345</v>
+        <v>56149</v>
       </c>
       <c r="E13">
-        <v>56149</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>4120.3</v>
+        <v>4115</v>
       </c>
       <c r="H13">
-        <v>991.7</v>
+        <v>735</v>
       </c>
       <c r="I13">
-        <v>2.212</v>
+        <v>1.768</v>
       </c>
     </row>
     <row r="14">
@@ -2018,28 +2018,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>4467</v>
       </c>
       <c r="C14">
-        <v>4677</v>
+        <v>118329</v>
       </c>
       <c r="D14">
-        <v>118329</v>
+        <v>58673</v>
       </c>
       <c r="E14">
-        <v>58673</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>4120.3</v>
+        <v>4115</v>
       </c>
       <c r="H14">
-        <v>556.7</v>
+        <v>352</v>
       </c>
       <c r="I14">
-        <v>1.242</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="15">
@@ -2047,28 +2047,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>3089</v>
       </c>
       <c r="C15">
-        <v>2933</v>
+        <v>120915</v>
       </c>
       <c r="D15">
-        <v>120915</v>
+        <v>26588</v>
       </c>
       <c r="E15">
-        <v>26588</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>2605.3</v>
+        <v>2611.3</v>
       </c>
       <c r="H15">
-        <v>327.7</v>
+        <v>477.7</v>
       </c>
       <c r="I15">
-        <v>0.715</v>
+        <v>1.149</v>
       </c>
     </row>
     <row r="16">
@@ -2076,28 +2076,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>4523</v>
       </c>
       <c r="C16">
-        <v>4733</v>
+        <v>133281</v>
       </c>
       <c r="D16">
-        <v>133281</v>
+        <v>68709</v>
       </c>
       <c r="E16">
-        <v>68709</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>4120.3</v>
+        <v>4115</v>
       </c>
       <c r="H16">
-        <v>612.7</v>
+        <v>408</v>
       </c>
       <c r="I16">
-        <v>1.367</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="17">
@@ -2105,28 +2105,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>4401</v>
       </c>
       <c r="C17">
-        <v>4607</v>
+        <v>135325</v>
       </c>
       <c r="D17">
-        <v>135325</v>
+        <v>48502</v>
       </c>
       <c r="E17">
-        <v>48502</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>4120.3</v>
+        <v>4115</v>
       </c>
       <c r="H17">
-        <v>486.7</v>
+        <v>286</v>
       </c>
       <c r="I17">
-        <v>1.085</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -2134,28 +2134,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>3586</v>
       </c>
       <c r="C18">
-        <v>3375</v>
+        <v>150982</v>
       </c>
       <c r="D18">
-        <v>150982</v>
+        <v>33792</v>
       </c>
       <c r="E18">
-        <v>33792</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>4120.3</v>
+        <v>4115</v>
       </c>
       <c r="H18">
-        <v>-745.3</v>
+        <v>-529</v>
       </c>
       <c r="I18">
-        <v>-1.662</v>
+        <v>-1.273</v>
       </c>
     </row>
     <row r="19">
@@ -2163,28 +2163,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>1949</v>
       </c>
       <c r="C19">
-        <v>1764</v>
+        <v>182381</v>
       </c>
       <c r="D19">
-        <v>182381</v>
+        <v>35875</v>
       </c>
       <c r="E19">
-        <v>35875</v>
+        <v>1.5</v>
       </c>
       <c r="F19">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>1469</v>
+        <v>1483.4</v>
       </c>
       <c r="H19">
-        <v>295</v>
+        <v>465.6</v>
       </c>
       <c r="I19">
-        <v>0.654</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="20">
@@ -2192,28 +2192,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>4219</v>
       </c>
       <c r="C20">
-        <v>4360</v>
+        <v>387887</v>
       </c>
       <c r="D20">
-        <v>387887</v>
+        <v>39480</v>
       </c>
       <c r="E20">
-        <v>39480</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>4120.3</v>
+        <v>4115</v>
       </c>
       <c r="H20">
-        <v>239.7</v>
+        <v>104</v>
       </c>
       <c r="I20">
-        <v>0.535</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="21">
@@ -2221,28 +2221,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>3469</v>
       </c>
       <c r="C21">
-        <v>3444</v>
+        <v>389167</v>
       </c>
       <c r="D21">
-        <v>389167</v>
+        <v>38821</v>
       </c>
       <c r="E21">
-        <v>38821</v>
+        <v>4</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>3362.8</v>
+        <v>3363.1</v>
       </c>
       <c r="H21">
-        <v>81.2</v>
+        <v>105.9</v>
       </c>
       <c r="I21">
-        <v>0.178</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="22">
@@ -2250,28 +2250,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2511</v>
       </c>
       <c r="C22">
-        <v>2285</v>
+        <v>396904</v>
       </c>
       <c r="D22">
-        <v>396904</v>
+        <v>38957</v>
       </c>
       <c r="E22">
-        <v>38957</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>1847.8</v>
+        <v>1859.4</v>
       </c>
       <c r="H22">
-        <v>437.2</v>
+        <v>651.6</v>
       </c>
       <c r="I22">
-        <v>0.961</v>
+        <v>1.568</v>
       </c>
     </row>
     <row r="23">
@@ -2279,28 +2279,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2750</v>
       </c>
       <c r="C23">
-        <v>2734</v>
+        <v>459473</v>
       </c>
       <c r="D23">
-        <v>459473</v>
+        <v>47320</v>
       </c>
       <c r="E23">
-        <v>47320</v>
+        <v>3</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>2605.3</v>
+        <v>2611.3</v>
       </c>
       <c r="H23">
-        <v>128.7</v>
+        <v>138.7</v>
       </c>
       <c r="I23">
-        <v>0.281</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="24">
@@ -2308,28 +2308,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>2789</v>
       </c>
       <c r="C24">
-        <v>2496</v>
+        <v>527877</v>
       </c>
       <c r="D24">
-        <v>527877</v>
+        <v>51200</v>
       </c>
       <c r="E24">
-        <v>51200</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>1847.8</v>
+        <v>1859.4</v>
       </c>
       <c r="H24">
-        <v>648.2</v>
+        <v>929.6</v>
       </c>
       <c r="I24">
-        <v>1.425</v>
+        <v>2.237</v>
       </c>
     </row>
     <row r="25">
@@ -2337,28 +2337,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2916</v>
       </c>
       <c r="C25">
-        <v>2631</v>
+        <v>27486</v>
       </c>
       <c r="D25">
-        <v>27486</v>
+        <v>110148</v>
       </c>
       <c r="E25">
-        <v>110148</v>
+        <v>4</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>3362.8</v>
+        <v>3363.1</v>
       </c>
       <c r="H25">
-        <v>-731.8</v>
+        <v>-447.1</v>
       </c>
       <c r="I25">
-        <v>-1.604</v>
+        <v>-1.076</v>
       </c>
     </row>
     <row r="26">
@@ -2366,28 +2366,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2267</v>
       </c>
       <c r="C26">
-        <v>2165</v>
+        <v>35436</v>
       </c>
       <c r="D26">
-        <v>35436</v>
+        <v>64938</v>
       </c>
       <c r="E26">
-        <v>64938</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>2605.3</v>
+        <v>2611.3</v>
       </c>
       <c r="H26">
-        <v>-440.3</v>
+        <v>-344.3</v>
       </c>
       <c r="I26">
-        <v>-0.96</v>
+        <v>-0.828</v>
       </c>
     </row>
     <row r="27">
@@ -2395,28 +2395,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>3139</v>
       </c>
       <c r="C27">
-        <v>2869</v>
+        <v>36788</v>
       </c>
       <c r="D27">
-        <v>36788</v>
+        <v>78608</v>
       </c>
       <c r="E27">
-        <v>78608</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>4120.3</v>
+        <v>4115</v>
       </c>
       <c r="H27">
-        <v>-1251.3</v>
+        <v>-976</v>
       </c>
       <c r="I27">
-        <v>-2.791</v>
+        <v>-2.348</v>
       </c>
     </row>
     <row r="28">
@@ -2424,28 +2424,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>1939</v>
       </c>
       <c r="C28">
-        <v>1926</v>
+        <v>65415</v>
       </c>
       <c r="D28">
-        <v>65415</v>
+        <v>50281</v>
       </c>
       <c r="E28">
-        <v>50281</v>
+        <v>2.5</v>
       </c>
       <c r="F28">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>2226.6</v>
+        <v>2235.3</v>
       </c>
       <c r="H28">
-        <v>-300.6</v>
+        <v>-296.3</v>
       </c>
       <c r="I28">
-        <v>-0.657</v>
+        <v>-0.713</v>
       </c>
     </row>
     <row r="29">
@@ -2453,28 +2453,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>3668</v>
       </c>
       <c r="C29">
-        <v>3291</v>
+        <v>66395</v>
       </c>
       <c r="D29">
-        <v>66395</v>
+        <v>82936</v>
       </c>
       <c r="E29">
-        <v>82936</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>4120.3</v>
+        <v>4115</v>
       </c>
       <c r="H29">
-        <v>-829.3</v>
+        <v>-447</v>
       </c>
       <c r="I29">
-        <v>-1.85</v>
+        <v>-1.076</v>
       </c>
     </row>
     <row r="30">
@@ -2482,28 +2482,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>2645</v>
       </c>
       <c r="C30">
-        <v>2302</v>
+        <v>80210</v>
       </c>
       <c r="D30">
-        <v>80210</v>
+        <v>58287</v>
       </c>
       <c r="E30">
-        <v>58287</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>2605.3</v>
+        <v>2611.3</v>
       </c>
       <c r="H30">
-        <v>-303.3</v>
+        <v>33.7</v>
       </c>
       <c r="I30">
-        <v>-0.662</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="31">
@@ -2511,28 +2511,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>1878</v>
       </c>
       <c r="C31">
-        <v>1913</v>
+        <v>81438</v>
       </c>
       <c r="D31">
-        <v>81438</v>
+        <v>65130</v>
       </c>
       <c r="E31">
-        <v>65130</v>
+        <v>2.5</v>
       </c>
       <c r="F31">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>2226.6</v>
+        <v>2235.3</v>
       </c>
       <c r="H31">
-        <v>-313.6</v>
+        <v>-357.3</v>
       </c>
       <c r="I31">
-        <v>-0.6860000000000001</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="32">
@@ -2540,28 +2540,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>1556</v>
       </c>
       <c r="C32">
-        <v>1681</v>
+        <v>105833</v>
       </c>
       <c r="D32">
-        <v>105833</v>
+        <v>88587</v>
       </c>
       <c r="E32">
-        <v>88587</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>1847.8</v>
+        <v>1859.4</v>
       </c>
       <c r="H32">
-        <v>-166.8</v>
+        <v>-303.4</v>
       </c>
       <c r="I32">
-        <v>-0.367</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="33">
@@ -2569,28 +2569,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="C33">
-        <v>1272</v>
+        <v>109139</v>
       </c>
       <c r="D33">
-        <v>109139</v>
+        <v>106508</v>
       </c>
       <c r="E33">
-        <v>106508</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>1090.3</v>
+        <v>1107.5</v>
       </c>
       <c r="H33">
-        <v>181.7</v>
+        <v>-89.5</v>
       </c>
       <c r="I33">
-        <v>0.408</v>
+        <v>-0.215</v>
       </c>
     </row>
     <row r="34">
@@ -2598,28 +2598,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="C34">
-        <v>2128</v>
+        <v>110247</v>
       </c>
       <c r="D34">
-        <v>110247</v>
+        <v>73393</v>
       </c>
       <c r="E34">
-        <v>73393</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>2605.3</v>
+        <v>2611.3</v>
       </c>
       <c r="H34">
-        <v>-477.3</v>
+        <v>-451.3</v>
       </c>
       <c r="I34">
-        <v>-1.041</v>
+        <v>-1.086</v>
       </c>
     </row>
     <row r="35">
@@ -2627,28 +2627,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>2441</v>
       </c>
       <c r="C35">
-        <v>2362</v>
+        <v>115501</v>
       </c>
       <c r="D35">
-        <v>115501</v>
+        <v>66667</v>
       </c>
       <c r="E35">
-        <v>66667</v>
+        <v>3.5</v>
       </c>
       <c r="F35">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>2984.1</v>
+        <v>2987.2</v>
       </c>
       <c r="H35">
-        <v>-622.1</v>
+        <v>-546.2</v>
       </c>
       <c r="I35">
-        <v>-1.358</v>
+        <v>-1.314</v>
       </c>
     </row>
     <row r="36">
@@ -2656,28 +2656,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>1950</v>
       </c>
       <c r="C36">
-        <v>2069</v>
+        <v>121059</v>
       </c>
       <c r="D36">
-        <v>121059</v>
+        <v>56754</v>
       </c>
       <c r="E36">
-        <v>56754</v>
+        <v>3</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>2605.3</v>
+        <v>2611.3</v>
       </c>
       <c r="H36">
-        <v>-536.3</v>
+        <v>-661.3</v>
       </c>
       <c r="I36">
-        <v>-1.17</v>
+        <v>-1.591</v>
       </c>
     </row>
     <row r="37">
@@ -2685,28 +2685,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>848</v>
       </c>
       <c r="C37">
-        <v>1059</v>
+        <v>125624</v>
       </c>
       <c r="D37">
-        <v>125624</v>
+        <v>60894</v>
       </c>
       <c r="E37">
-        <v>60894</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>1090.3</v>
+        <v>1107.5</v>
       </c>
       <c r="H37">
-        <v>-31.3</v>
+        <v>-259.5</v>
       </c>
       <c r="I37">
-        <v>-0.07000000000000001</v>
+        <v>-0.624</v>
       </c>
     </row>
     <row r="38">
@@ -2714,28 +2714,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>1560</v>
       </c>
       <c r="C38">
-        <v>1691</v>
+        <v>127477</v>
       </c>
       <c r="D38">
-        <v>127477</v>
+        <v>73027</v>
       </c>
       <c r="E38">
-        <v>73027</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>1847.8</v>
+        <v>1859.4</v>
       </c>
       <c r="H38">
-        <v>-156.8</v>
+        <v>-299.4</v>
       </c>
       <c r="I38">
-        <v>-0.345</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="39">
@@ -2743,28 +2743,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>1443</v>
       </c>
       <c r="C39">
-        <v>1399</v>
+        <v>156559</v>
       </c>
       <c r="D39">
-        <v>156559</v>
+        <v>63554</v>
       </c>
       <c r="E39">
-        <v>63554</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>1090.3</v>
+        <v>1107.5</v>
       </c>
       <c r="H39">
-        <v>308.7</v>
+        <v>335.5</v>
       </c>
       <c r="I39">
-        <v>0.6929999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -2772,28 +2772,28 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>1555</v>
       </c>
       <c r="C40">
-        <v>1695</v>
+        <v>163039</v>
       </c>
       <c r="D40">
-        <v>163039</v>
+        <v>36416</v>
       </c>
       <c r="E40">
-        <v>36416</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>1847.8</v>
+        <v>1859.4</v>
       </c>
       <c r="H40">
-        <v>-152.8</v>
+        <v>-304.4</v>
       </c>
       <c r="I40">
-        <v>-0.336</v>
+        <v>-0.732</v>
       </c>
     </row>
     <row r="41">
@@ -2801,28 +2801,28 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1365</v>
       </c>
       <c r="C41">
-        <v>1502</v>
+        <v>171086</v>
       </c>
       <c r="D41">
-        <v>171086</v>
+        <v>63085</v>
       </c>
       <c r="E41">
-        <v>63085</v>
+        <v>1.5</v>
       </c>
       <c r="F41">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>1469</v>
+        <v>1483.4</v>
       </c>
       <c r="H41">
-        <v>33</v>
+        <v>-118.4</v>
       </c>
       <c r="I41">
-        <v>0.073</v>
+        <v>-0.285</v>
       </c>
     </row>
     <row r="42">
@@ -2830,28 +2830,28 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2145</v>
       </c>
       <c r="C42">
-        <v>2148</v>
+        <v>192373</v>
       </c>
       <c r="D42">
-        <v>192373</v>
+        <v>44851</v>
       </c>
       <c r="E42">
-        <v>44851</v>
+        <v>3</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>2605.3</v>
+        <v>2611.3</v>
       </c>
       <c r="H42">
-        <v>-457.3</v>
+        <v>-466.3</v>
       </c>
       <c r="I42">
-        <v>-0.998</v>
+        <v>-1.122</v>
       </c>
     </row>
     <row r="43">
@@ -2859,28 +2859,28 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>2343</v>
       </c>
       <c r="C43">
-        <v>2033</v>
+        <v>193961</v>
       </c>
       <c r="D43">
-        <v>193961</v>
+        <v>69780</v>
       </c>
       <c r="E43">
-        <v>69780</v>
+        <v>2.5</v>
       </c>
       <c r="F43">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>2226.6</v>
+        <v>2235.3</v>
       </c>
       <c r="H43">
-        <v>-193.6</v>
+        <v>107.7</v>
       </c>
       <c r="I43">
-        <v>-0.423</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="44">
@@ -2888,28 +2888,28 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>1169</v>
       </c>
       <c r="C44">
-        <v>1460</v>
+        <v>250989</v>
       </c>
       <c r="D44">
-        <v>250989</v>
+        <v>60684</v>
       </c>
       <c r="E44">
-        <v>60684</v>
+        <v>1.5</v>
       </c>
       <c r="F44">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>1469</v>
+        <v>1483.4</v>
       </c>
       <c r="H44">
-        <v>-9</v>
+        <v>-314.4</v>
       </c>
       <c r="I44">
-        <v>-0.02</v>
+        <v>-0.756</v>
       </c>
     </row>
     <row r="45">
@@ -2917,28 +2917,28 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>1476</v>
       </c>
       <c r="C45">
-        <v>1690</v>
+        <v>380860</v>
       </c>
       <c r="D45">
-        <v>380860</v>
+        <v>62821</v>
       </c>
       <c r="E45">
-        <v>62821</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>1847.8</v>
+        <v>1859.4</v>
       </c>
       <c r="H45">
-        <v>-157.8</v>
+        <v>-383.4</v>
       </c>
       <c r="I45">
-        <v>-0.347</v>
+        <v>-0.922</v>
       </c>
     </row>
     <row r="46">
@@ -2946,28 +2946,28 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>2232</v>
       </c>
       <c r="C46">
-        <v>2186</v>
+        <v>386399</v>
       </c>
       <c r="D46">
-        <v>386399</v>
+        <v>44625</v>
       </c>
       <c r="E46">
-        <v>44625</v>
+        <v>3</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>2605.3</v>
+        <v>2611.3</v>
       </c>
       <c r="H46">
-        <v>-419.3</v>
+        <v>-379.3</v>
       </c>
       <c r="I46">
-        <v>-0.915</v>
+        <v>-0.912</v>
       </c>
     </row>
   </sheetData>
